--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="C32" t="n">
         <v>3.5</v>
       </c>
       <c r="D32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,97 +448,151 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.25</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -548,7 +602,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -558,7 +612,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -568,7 +622,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -578,7 +632,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -588,7 +642,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -598,7 +652,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -608,7 +662,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -618,7 +672,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -628,7 +682,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -638,7 +692,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -648,7 +702,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -658,7 +712,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -668,7 +722,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -678,7 +732,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -688,7 +742,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -698,7 +752,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -708,7 +762,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -718,7 +772,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -728,7 +782,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -738,7 +792,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -748,17 +802,117 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
+      <c r="B42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,135 +464,87 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3.1</v>
-      </c>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.15</v>
-      </c>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.75</v>
-      </c>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.9</v>
-      </c>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7.5</v>
-      </c>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.5</v>
-      </c>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.5</v>
-      </c>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.25</v>
-      </c>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -602,7 +554,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -612,7 +564,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -622,7 +574,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -632,7 +584,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -642,7 +594,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -652,7 +604,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -662,7 +614,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -672,7 +624,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -682,7 +634,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -692,7 +644,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -702,7 +654,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -712,7 +664,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -722,7 +674,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -732,7 +684,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -742,7 +694,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -752,7 +704,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -762,7 +714,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -772,7 +724,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -782,7 +734,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -792,7 +744,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -802,7 +754,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -812,106 +764,16 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B33" t="n">
         <v>1.8</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C33" t="n">
         <v>3.6</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D33" t="n">
         <v>4.1</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,99 +452,147 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.25</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -554,7 +602,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -564,7 +612,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -574,7 +622,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -584,7 +632,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -594,7 +642,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -604,7 +652,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -614,7 +662,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -624,7 +672,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -634,7 +682,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -644,7 +692,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -654,7 +702,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -664,7 +712,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -674,7 +722,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -684,7 +732,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -694,7 +742,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -704,7 +752,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -714,7 +762,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -724,7 +772,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -734,7 +782,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -744,7 +792,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -754,7 +802,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -764,16 +812,96 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B41" t="n">
         <v>1.8</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C41" t="n">
         <v>3.6</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D41" t="n">
         <v>4.1</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="C4" t="n">
         <v>3.5</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="C7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>7.5</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D8" t="n">
         <v>4.5</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="C10" t="n">
         <v>3.5</v>
@@ -592,137 +592,215 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.75</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.95</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.36</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>34</v>
+      </c>
+      <c r="C22" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.02</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.48</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -732,178 +810,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C41" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D41" t="n">
-        <v>4.1</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="C4" t="n">
         <v>3.5</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="C7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>7.5</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D8" t="n">
         <v>4.5</v>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C9" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="10">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="C10" t="n">
         <v>3.5</v>
@@ -592,97 +592,151 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.75</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.95</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -692,218 +746,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hzyf0b9b</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>CpiTEcOi</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>8CpxDyg4</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C41" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D41" t="n">
-        <v>4.1</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
         <v>4.33</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="C5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D5" t="n">
         <v>4.75</v>
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="D7" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="8">
@@ -586,7 +586,7 @@
         <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
@@ -602,7 +602,7 @@
         <v>3.5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="C13" t="n">
         <v>3.8</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="14">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="C14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="C15" t="n">
         <v>4.33</v>
       </c>
       <c r="D15" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16">
@@ -724,34 +724,14 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="C19" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="D19" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6u6i5pie</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,289 +448,97 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="C3" t="n">
         <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="C7" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>SxFxJ44k</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>djSMofvg</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>U3QUqY85</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>AgAeVYgC</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="C15" t="n">
         <v>4.33</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C19" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="D19" t="n">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,97 +448,177 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="C3" t="n">
         <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D7" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,176 +448,144 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="C3" t="n">
         <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="C5" t="n">
         <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="C8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="D8" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="C10" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="n">
         <v>11</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="C3" t="n">
         <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +490,7 @@
         <v>3.8</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="C6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C7" t="n">
         <v>3.7</v>
       </c>
-      <c r="C7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="D7" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="C8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9">

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,145 +448,241 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="C2" t="n">
         <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.62</v>
+        <v>3.9</v>
       </c>
       <c r="C6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D7" t="n">
         <v>4.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,241 +448,33 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
           <t>2T6mXfPa</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B3" t="n">
         <v>1.2</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C3" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D3" t="n">
         <v>11</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>zsmd0ggn</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UwsvBA74</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vZqDdBhB</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>r7j4bXNb</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>WSMotj8U</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>tI0qkTpo</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>x4pn9lxH</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,33 +448,145 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.2</v>
+        <v>2.88</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="C2" t="n">
         <v>5.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="C3" t="n">
         <v>4.1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="C6" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="C7" t="n">
         <v>3.6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="D8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="C9" t="n">
         <v>3.6</v>
       </c>
       <c r="D9" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,157 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="D10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,289 +448,33 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zsmd0ggn</t>
+          <t>CnrLfkNN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>UwsvBA74</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>vZqDdBhB</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>r7j4bXNb</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WSMotj8U</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tI0qkTpo</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>x4pn9lxH</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CnrLfkNN</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
           <t>8OhVCWxh</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C3" t="n">
         <v>3.7</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D3" t="n">
         <v>3.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>dCL13J5e</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pY1dP0SE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>QNoNA1DL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hvFA1cz8</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>AeNg5uyq</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>IcrFCNr9</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Uy2KjtMk</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>2k0SlKj2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,33 +448,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="C2" t="n">
         <v>3.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C19" t="n">
         <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,289 +448,129 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dCL13J5e</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="C2" t="n">
         <v>3.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pY1dP0SE</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="C3" t="n">
         <v>3.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QNoNA1DL</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hvFA1cz8</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AeNg5uyq</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>1.75</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.38</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IcrFCNr9</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3.9</v>
+        <v>5.75</v>
       </c>
       <c r="D7" t="n">
-        <v>4.33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Uy2KjtMk</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="C8" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="D8" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2k0SlKj2</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.35</v>
+        <v>5.75</v>
       </c>
       <c r="C9" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C15" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,33 +448,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>CIlrT3pm</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D3" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C10" t="n">
         <v>3.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         <v>1.25</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         <v>2.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         <v>1.4</v>
       </c>
       <c r="C6" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="D6" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +535,7 @@
         <v>3.2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D7" t="n">
         <v>2.05</v>
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="C8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D8" t="n">
         <v>4.2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.1</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C9" t="n">
         <v>4.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="10">
@@ -580,157 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="C10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D11" t="n">
         <v>2.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="C12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ENOasf5c</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zwD8uYZ9</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D19" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,144 +448,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rsNyMnwK</t>
+          <t>pWnjRsFa</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.25</v>
+        <v>4.33</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
           <t>bFO8E4Vg</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C3" t="n">
         <v>3.8</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D3" t="n">
         <v>2.7</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,33 +448,241 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>UajsPCkT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>tbtaPLqC</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>2.4</v>
       </c>
-      <c r="C3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.7</v>
+      <c r="C7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,241 +448,193 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.09</v>
+        <v>5.5</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.7</v>
+        <v>6.25</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="D5" t="n">
-        <v>2.15</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.33</v>
+        <v>1.8</v>
       </c>
       <c r="C8" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="C9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.53</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="C11" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="C12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="C13" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,193 +448,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.33</v>
+        <v>1.29</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.53</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="C4" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="D4" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="C5" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="D5" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.83</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="C12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="C13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C18" t="n">
         <v>3.3</v>
       </c>
-      <c r="D13" t="n">
-        <v>3.4</v>
+      <c r="D18" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="C2" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +474,7 @@
         <v>3.5</v>
       </c>
       <c r="D3" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="C4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="C7" t="n">
         <v>3.7</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="8">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="10">
@@ -586,7 +586,7 @@
         <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="C11" t="n">
         <v>3.7</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         <v>5.75</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -682,7 +682,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="17">
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="18">

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -455,10 +455,10 @@
         <v>1.3</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="C3" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         <v>1.44</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="D4" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         <v>1.67</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="C7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         <v>1.36</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="C9" t="n">
         <v>3.3</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
         <v>3.6</v>
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="C11" t="n">
         <v>3.7</v>
       </c>
       <c r="D11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,289 +448,33 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="C2" t="n">
-        <v>5.75</v>
+        <v>3.3</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>r3GGwC4M</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>2mcmYkSq</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>nBwH6AY8</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
           <t>rPiijklS</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B3" t="n">
         <v>2.05</v>
       </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C3" t="n">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>4E8uaJWa</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>x0haJmIE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ELNeaSQr</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Mku6FvHt</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="D3" t="n">
         <v>3.4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rwXP4l3L</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="D15" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>MiACepQ7</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WQadeyWO</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>9</v>
-      </c>
-      <c r="C17" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ABBmcc1C</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>zyC4c6ee</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,33 +448,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D14" t="n">
         <v>3.6</v>
       </c>
-      <c r="D3" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D16" t="n">
         <v>3.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +474,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="C4" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         <v>1.25</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C7" t="n">
         <v>5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5.25</v>
       </c>
       <c r="D7" t="n">
         <v>1.5</v>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>9.5</v>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="C9" t="n">
         <v>3.3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="10">
@@ -580,157 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
         <v>3.1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IHYEDIog</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>jVWMBdG5</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>485V7EFU</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8MVuSH0n</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2q7yHiho</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>GnZmQeVb</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>raQ4MDUN</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,145 +448,289 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>IHYEDIog</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="D2" t="n">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>jVWMBdG5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6</v>
+        <v>1.18</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>1.91</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>485V7EFU</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="C4" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>8MVuSH0n</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rwXP4l3L</t>
+          <t>2q7yHiho</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MiACepQ7</t>
+          <t>AoSdOZaB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.25</v>
+        <v>1.95</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WQadeyWO</t>
+          <t>dr2N9zoI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>2.25</v>
       </c>
       <c r="C8" t="n">
-        <v>9.5</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>GnZmQeVb</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="D9" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>raQ4MDUN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="C10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>v3DAZKP9</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xMovyDqH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C19" t="n">
         <v>3.5</v>
       </c>
-      <c r="D10" t="n">
-        <v>3.1</v>
+      <c r="D19" t="n">
+        <v>2.55</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="D2" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +471,7 @@
         <v>1.18</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
@@ -487,7 +487,7 @@
         <v>1.33</v>
       </c>
       <c r="C4" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="D4" t="n">
         <v>7.5</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="C5" t="n">
         <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="n">
         <v>2.45</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D7" t="n">
         <v>3.5</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -570,7 +570,7 @@
         <v>3.9</v>
       </c>
       <c r="D9" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="10">
@@ -580,157 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="C10" t="n">
         <v>3.8</v>
       </c>
       <c r="D10" t="n">
         <v>3.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>v3DAZKP9</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>biQrHC9r</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>11</v>
-      </c>
-      <c r="C14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YmumZjET</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>j5mWxZE4</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UkaNveph</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xMovyDqH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.55</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,145 +448,145 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="C2" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.18</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="C4" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="D4" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.83</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="D6" t="n">
-        <v>2.45</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="C7" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="C9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="D9" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/germany/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         <v>2.38</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="C4" t="n">
         <v>3.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="C5" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="C6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="C8" t="n">
         <v>3.75</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="C9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,125 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="C10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2qNaDU87</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E38ZP7hD</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fwAoyY0E</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SrjMmBpK</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6w5RRTN0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.75</v>
       </c>
     </row>
   </sheetData>
